--- a/test-documentation.xlsx
+++ b/test-documentation.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Unit Tests" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1252" uniqueCount="604">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1241" uniqueCount="604">
   <si>
     <t>testCaseId</t>
   </si>
@@ -2046,7 +2046,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -2058,6 +2058,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2402,7 +2405,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M37"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.796875" customWidth="1"/>
     <col min="2" max="2" width="45.796875" customWidth="1"/>
@@ -2417,7 +2420,7 @@
     <col min="13" max="13" width="15.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2458,7 +2461,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -2499,7 +2502,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -2540,7 +2543,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -2581,7 +2584,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>39</v>
       </c>
@@ -2622,7 +2625,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>45</v>
       </c>
@@ -2663,7 +2666,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>51</v>
       </c>
@@ -2704,7 +2707,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>58</v>
       </c>
@@ -2745,7 +2748,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>64</v>
       </c>
@@ -2786,7 +2789,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>71</v>
       </c>
@@ -2827,7 +2830,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>78</v>
       </c>
@@ -2868,7 +2871,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>84</v>
       </c>
@@ -2909,7 +2912,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>90</v>
       </c>
@@ -2950,7 +2953,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>96</v>
       </c>
@@ -2991,7 +2994,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>101</v>
       </c>
@@ -3032,7 +3035,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>107</v>
       </c>
@@ -3073,7 +3076,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>114</v>
       </c>
@@ -3114,7 +3117,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>120</v>
       </c>
@@ -3155,7 +3158,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>125</v>
       </c>
@@ -3196,7 +3199,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>131</v>
       </c>
@@ -3237,7 +3240,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>137</v>
       </c>
@@ -3278,7 +3281,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>143</v>
       </c>
@@ -3319,7 +3322,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>147</v>
       </c>
@@ -3360,7 +3363,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>152</v>
       </c>
@@ -3376,8 +3379,8 @@
       <c r="E24" t="s">
         <v>17</v>
       </c>
-      <c r="F24" t="s">
-        <v>18</v>
+      <c r="F24" s="6">
+        <v>46056</v>
       </c>
       <c r="G24" t="s">
         <v>154</v>
@@ -3401,7 +3404,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>157</v>
       </c>
@@ -3417,8 +3420,8 @@
       <c r="E25" t="s">
         <v>17</v>
       </c>
-      <c r="F25" t="s">
-        <v>18</v>
+      <c r="F25" s="6">
+        <v>46056</v>
       </c>
       <c r="G25" t="s">
         <v>159</v>
@@ -3442,7 +3445,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>163</v>
       </c>
@@ -3458,8 +3461,8 @@
       <c r="E26" t="s">
         <v>17</v>
       </c>
-      <c r="F26" t="s">
-        <v>18</v>
+      <c r="F26" s="6">
+        <v>46056</v>
       </c>
       <c r="G26" t="s">
         <v>165</v>
@@ -3483,7 +3486,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>168</v>
       </c>
@@ -3524,7 +3527,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>176</v>
       </c>
@@ -3565,7 +3568,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>183</v>
       </c>
@@ -3606,7 +3609,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>188</v>
       </c>
@@ -3647,7 +3650,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>193</v>
       </c>
@@ -3688,7 +3691,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>200</v>
       </c>
@@ -3729,7 +3732,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="33" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>207</v>
       </c>
@@ -3770,7 +3773,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>214</v>
       </c>
@@ -3786,8 +3789,8 @@
       <c r="E34" t="s">
         <v>17</v>
       </c>
-      <c r="F34" t="s">
-        <v>18</v>
+      <c r="F34" s="6">
+        <v>46056</v>
       </c>
       <c r="G34" t="s">
         <v>216</v>
@@ -3811,7 +3814,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>220</v>
       </c>
@@ -3827,8 +3830,8 @@
       <c r="E35" t="s">
         <v>17</v>
       </c>
-      <c r="F35" t="s">
-        <v>18</v>
+      <c r="F35" s="6">
+        <v>46056</v>
       </c>
       <c r="G35" t="s">
         <v>171</v>
@@ -3852,7 +3855,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="36" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>223</v>
       </c>
@@ -3868,8 +3871,8 @@
       <c r="E36" t="s">
         <v>17</v>
       </c>
-      <c r="F36" t="s">
-        <v>18</v>
+      <c r="F36" s="6">
+        <v>46056</v>
       </c>
       <c r="G36" t="s">
         <v>225</v>
@@ -3893,7 +3896,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="37" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>228</v>
       </c>
@@ -3909,8 +3912,8 @@
       <c r="E37" t="s">
         <v>17</v>
       </c>
-      <c r="F37" t="s">
-        <v>18</v>
+      <c r="F37" s="6">
+        <v>46056</v>
       </c>
       <c r="G37" t="s">
         <v>230</v>
@@ -3938,7 +3941,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:M37" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:M23 A27:M33 A24:E24 G24:M24 A25:E25 G25:M25 A26:E26 G26:M26 A37:E37 A34:E34 G34:M34 A35:E35 G35:M35 A36:E36 G36:M36 G37:M37" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3946,7 +3949,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.796875" customWidth="1"/>
     <col min="2" max="2" width="45.796875" customWidth="1"/>
@@ -3960,7 +3963,7 @@
     <col min="12" max="13" width="15.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4001,7 +4004,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>236</v>
       </c>
@@ -4042,7 +4045,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>244</v>
       </c>
@@ -4083,7 +4086,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>249</v>
       </c>
@@ -4124,7 +4127,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>254</v>
       </c>
@@ -4165,7 +4168,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>261</v>
       </c>
@@ -4206,7 +4209,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>267</v>
       </c>
@@ -4247,7 +4250,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>274</v>
       </c>
@@ -4288,7 +4291,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>281</v>
       </c>
@@ -4329,7 +4332,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>288</v>
       </c>
@@ -4370,7 +4373,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>295</v>
       </c>
@@ -4411,7 +4414,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>302</v>
       </c>
@@ -4452,7 +4455,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>309</v>
       </c>
@@ -4504,7 +4507,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.796875" customWidth="1"/>
     <col min="2" max="2" width="45.796875" customWidth="1"/>
@@ -4518,7 +4521,7 @@
     <col min="12" max="13" width="15.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4559,7 +4562,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>316</v>
       </c>
@@ -4600,7 +4603,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>322</v>
       </c>
@@ -4641,7 +4644,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>328</v>
       </c>
@@ -4682,7 +4685,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>335</v>
       </c>
@@ -4723,7 +4726,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>342</v>
       </c>
@@ -4764,7 +4767,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>348</v>
       </c>
@@ -4805,7 +4808,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>355</v>
       </c>
@@ -4846,7 +4849,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>362</v>
       </c>
@@ -4887,7 +4890,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>369</v>
       </c>
@@ -4928,7 +4931,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>375</v>
       </c>
@@ -4969,7 +4972,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>381</v>
       </c>
@@ -5010,7 +5013,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>388</v>
       </c>
@@ -5051,7 +5054,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>393</v>
       </c>
@@ -5092,7 +5095,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>399</v>
       </c>
@@ -5133,7 +5136,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>405</v>
       </c>
@@ -5174,7 +5177,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>412</v>
       </c>
@@ -5215,7 +5218,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>418</v>
       </c>
@@ -5256,7 +5259,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>426</v>
       </c>
@@ -5297,7 +5300,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>431</v>
       </c>
@@ -5338,7 +5341,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>437</v>
       </c>
@@ -5379,7 +5382,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>443</v>
       </c>
@@ -5420,7 +5423,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>451</v>
       </c>
@@ -5461,7 +5464,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>458</v>
       </c>
@@ -5513,7 +5516,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M18"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.796875" customWidth="1"/>
     <col min="2" max="2" width="45.796875" customWidth="1"/>
@@ -5527,7 +5530,7 @@
     <col min="12" max="13" width="15.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5568,7 +5571,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>465</v>
       </c>
@@ -5609,7 +5612,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>472</v>
       </c>
@@ -5650,7 +5653,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>476</v>
       </c>
@@ -5691,7 +5694,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>482</v>
       </c>
@@ -5732,7 +5735,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>488</v>
       </c>
@@ -5773,7 +5776,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>495</v>
       </c>
@@ -5814,7 +5817,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>503</v>
       </c>
@@ -5855,7 +5858,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>508</v>
       </c>
@@ -5896,7 +5899,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>513</v>
       </c>
@@ -5937,7 +5940,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>518</v>
       </c>
@@ -5978,7 +5981,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>524</v>
       </c>
@@ -6019,7 +6022,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>532</v>
       </c>
@@ -6060,7 +6063,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>538</v>
       </c>
@@ -6101,7 +6104,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>544</v>
       </c>
@@ -6117,8 +6120,8 @@
       <c r="E15" t="s">
         <v>17</v>
       </c>
-      <c r="F15" t="s">
-        <v>18</v>
+      <c r="F15" s="6">
+        <v>46056</v>
       </c>
       <c r="G15" t="s">
         <v>546</v>
@@ -6142,7 +6145,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>548</v>
       </c>
@@ -6158,8 +6161,8 @@
       <c r="E16" t="s">
         <v>17</v>
       </c>
-      <c r="F16" t="s">
-        <v>18</v>
+      <c r="F16" s="6">
+        <v>46056</v>
       </c>
       <c r="G16" t="s">
         <v>550</v>
@@ -6183,7 +6186,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>553</v>
       </c>
@@ -6199,8 +6202,8 @@
       <c r="E17" t="s">
         <v>17</v>
       </c>
-      <c r="F17" t="s">
-        <v>18</v>
+      <c r="F17" s="6">
+        <v>46056</v>
       </c>
       <c r="G17" t="s">
         <v>555</v>
@@ -6224,7 +6227,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>557</v>
       </c>
@@ -6240,8 +6243,8 @@
       <c r="E18" t="s">
         <v>17</v>
       </c>
-      <c r="F18" t="s">
-        <v>18</v>
+      <c r="F18" s="6">
+        <v>46056</v>
       </c>
       <c r="G18" t="s">
         <v>559</v>
@@ -6268,7 +6271,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:M18" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:M14 A18:E18 A15:E15 G15:M15 A16:E16 G16:M16 A17:E17 G17:M17 G18:M18" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -6276,7 +6279,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.796875" customWidth="1"/>
     <col min="2" max="2" width="50.796875" customWidth="1"/>
@@ -6290,7 +6293,7 @@
     <col min="16" max="16" width="12.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>562</v>
       </c>
@@ -6340,7 +6343,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>575</v>
       </c>
@@ -6388,7 +6391,7 @@
         <v>46055</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>585</v>
       </c>
@@ -6447,14 +6450,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.796875" customWidth="1"/>
     <col min="2" max="3" width="15.796875" customWidth="1"/>
     <col min="4" max="4" width="40.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>591</v>
       </c>
@@ -6468,7 +6471,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>595</v>
       </c>
@@ -6482,7 +6485,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>597</v>
       </c>
@@ -6496,7 +6499,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>599</v>
       </c>
@@ -6510,7 +6513,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>601</v>
       </c>
@@ -6524,7 +6527,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>603</v>
       </c>
